--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260709.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.65%</t>
+          <t>28.06%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>8.58%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.31%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.10%</t>
+          <t>6.29%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>5.37%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>147,491,691</t>
+          <t>87,355</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>87,355</t>
+          <t>9,090</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>9,090</t>
+          <t>22,170</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -990,112 +990,112 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>22,170</t>
+          <t>41,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>41,000</t>
+          <t>67,258</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>67,258</t>
+          <t>99,119,650</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>13,251</t>
+          <t>10,866</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>10,866</t>
+          <t>13,251</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1210,29 +1210,29 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,925,386</t>
+          <t>13,305</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1254,73 +1254,51 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>13,305</t>
+          <t>48,940</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>48,940</t>
+          <t>1,625,386</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>9,642,000</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
